--- a/data/trans_dic/IMC_inf_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 36,84</t>
+          <t>17,06; 37,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 49,05</t>
+          <t>22,29; 47,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,78; 57,4</t>
+          <t>31,19; 57,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 40,61</t>
+          <t>15,45; 38,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,11; 53,64</t>
+          <t>32,09; 55,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,34; 57,4</t>
+          <t>32,13; 59,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,31; 66,65</t>
+          <t>41,09; 66,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 34,9</t>
+          <t>14,88; 35,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,09; 41,47</t>
+          <t>26,7; 42,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,95; 50,45</t>
+          <t>31,38; 50,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,51; 58,52</t>
+          <t>38,64; 58,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,04; 33,51</t>
+          <t>17,77; 33,58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,91; 45,35</t>
+          <t>27,67; 44,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,13; 49,72</t>
+          <t>31,0; 48,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,95; 50,13</t>
+          <t>32,95; 50,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 37,69</t>
+          <t>12,22; 38,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,54; 57,04</t>
+          <t>40,78; 57,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,32; 56,28</t>
+          <t>38,62; 57,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,0; 63,52</t>
+          <t>46,5; 63,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,19; 56,35</t>
+          <t>35,2; 56,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,04; 48,78</t>
+          <t>36,85; 48,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,08; 49,85</t>
+          <t>37,05; 50,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,34; 54,64</t>
+          <t>41,73; 54,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,1; 43,91</t>
+          <t>21,6; 43,73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 31,06</t>
+          <t>13,81; 31,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,53; 62,96</t>
+          <t>41,29; 62,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,3; 40,41</t>
+          <t>18,7; 38,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,26; 38,77</t>
+          <t>19,26; 38,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,78; 48,77</t>
+          <t>31,75; 48,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,65; 61,26</t>
+          <t>41,11; 61,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,63; 47,44</t>
+          <t>28,37; 48,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,88; 63,04</t>
+          <t>39,68; 61,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,98; 37,4</t>
+          <t>24,39; 38,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,07; 58,18</t>
+          <t>43,83; 58,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,66; 41,24</t>
+          <t>26,34; 40,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,04; 47,41</t>
+          <t>32,18; 47,31</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,34; 50,24</t>
+          <t>31,48; 50,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 40,6</t>
+          <t>20,52; 41,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,32; 49,12</t>
+          <t>27,71; 48,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 41,39</t>
+          <t>16,54; 41,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,95; 48,35</t>
+          <t>30,06; 48,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,0; 64,37</t>
+          <t>42,62; 64,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,12; 59,32</t>
+          <t>37,48; 60,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 46,23</t>
+          <t>12,35; 44,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,66; 45,9</t>
+          <t>33,28; 46,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,42; 49,36</t>
+          <t>33,87; 50,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,98; 50,98</t>
+          <t>35,56; 51,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 39,91</t>
+          <t>17,93; 38,77</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,15; 66,27</t>
+          <t>38,07; 65,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 50,04</t>
+          <t>20,08; 49,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 47,39</t>
+          <t>19,9; 46,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,15; 46,29</t>
+          <t>23,71; 47,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,31; 74,01</t>
+          <t>47,8; 72,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,95; 62,09</t>
+          <t>32,45; 61,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,42; 47,42</t>
+          <t>22,61; 47,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,28; 58,81</t>
+          <t>32,72; 57,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,0; 66,55</t>
+          <t>48,28; 66,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,34; 51,75</t>
+          <t>29,8; 51,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,51; 43,65</t>
+          <t>25,83; 44,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,96; 49,58</t>
+          <t>32,28; 49,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,91; 34,83</t>
+          <t>15,79; 36,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,1; 57,36</t>
+          <t>33,47; 57,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,68; 43,82</t>
+          <t>20,38; 42,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,18; 37,83</t>
+          <t>15,09; 35,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,24; 60,45</t>
+          <t>38,77; 60,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,66; 47,98</t>
+          <t>25,77; 48,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,32; 61,51</t>
+          <t>37,3; 60,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,58; 49,18</t>
+          <t>25,59; 47,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,7; 45,97</t>
+          <t>30,33; 45,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,65; 49,29</t>
+          <t>31,87; 48,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,03; 48,69</t>
+          <t>31,92; 49,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,14; 40,06</t>
+          <t>23,5; 38,74</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,69; 37,52</t>
+          <t>23,61; 38,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,84; 47,9</t>
+          <t>32,24; 47,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,9; 36,71</t>
+          <t>22,6; 36,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,37; 42,47</t>
+          <t>25,98; 42,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,8; 46,96</t>
+          <t>32,71; 47,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,25; 62,59</t>
+          <t>47,68; 62,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,16; 43,02</t>
+          <t>27,65; 41,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,56; 51,7</t>
+          <t>32,85; 50,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,43; 40,46</t>
+          <t>30,2; 39,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42,21; 53,02</t>
+          <t>41,65; 53,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,14; 36,98</t>
+          <t>26,92; 37,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,9; 44,46</t>
+          <t>32,73; 44,19</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,86; 53,53</t>
+          <t>38,94; 53,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,23; 56,65</t>
+          <t>42,65; 57,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,49; 43,07</t>
+          <t>29,67; 42,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,02; 32,34</t>
+          <t>19,44; 32,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,31; 55,61</t>
+          <t>41,67; 55,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,03; 62,81</t>
+          <t>47,79; 62,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,94; 53,78</t>
+          <t>39,93; 53,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,51; 43,95</t>
+          <t>29,92; 43,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41,96; 51,8</t>
+          <t>42,01; 52,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,46; 57,68</t>
+          <t>47,45; 57,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,43; 46,04</t>
+          <t>36,95; 46,45</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,13; 36,4</t>
+          <t>26,55; 36,41</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32,29; 38,59</t>
+          <t>32,38; 38,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38,97; 45,71</t>
+          <t>38,24; 45,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,75; 38,2</t>
+          <t>31,34; 38,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23,63; 32,22</t>
+          <t>24,07; 32,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42,26; 48,48</t>
+          <t>42,27; 48,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,95; 54,25</t>
+          <t>46,84; 53,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,18; 48,25</t>
+          <t>41,28; 48,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,86; 42,9</t>
+          <t>35,21; 43,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,08; 42,61</t>
+          <t>38,2; 42,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43,86; 49,11</t>
+          <t>43,85; 48,69</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37,54; 42,22</t>
+          <t>37,7; 42,69</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,66; 36,92</t>
+          <t>30,95; 36,93</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11994</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12022</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16259</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15067</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20686</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18529</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19102</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14366</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>32680</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30551</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35361</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>29433</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8027; 17542</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7770; 16617</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11480; 21082</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8787; 22038</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15604; 26855</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13123; 24160</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14541; 23586</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9001; 21296</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>25543; 40505</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>23756; 38122</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>27895; 42174</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>20864; 39423</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>27667</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29267</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34901</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31514</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44379</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>37465</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49545</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>50991</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>72046</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>66732</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>84446</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>82506</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>21465; 34651</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22905; 36027</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>27835; 42787</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14536; 45969</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>36957; 51700</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>30769; 45415</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>41949; 57241</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>39811; 63876</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>61988; 82316</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>56899; 76967</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>72899; 95172</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>50111; 101471</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12166</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29742</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16297</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14231</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24979</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30677</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23156</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>28730</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>37144</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>60419</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>39454</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>42961</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7859; 18070</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23930; 36294</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10611; 22053</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9685; 19169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19949; 30762</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24771; 37223</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17503; 29741</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22446; 34669</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>29208; 46113</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>51812; 69597</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>31202; 48363</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>34386; 50561</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>26901</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16172</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19937</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13195</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28875</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29587</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18655</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>55776</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45759</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>47760</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>31850</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>20890; 33515</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11101; 22580</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14603; 25669</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7811; 19786</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>22269; 35993</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>23651; 35828</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>21547; 34786</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7694; 27848</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>46742; 64995</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>37113; 54921</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>39181; 57285</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>19635; 42465</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>19142</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8692</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11786</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11799</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24549</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14097</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13207</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18030</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>43691</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22790</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24993</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>29830</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13955; 23891</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5289; 13034</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7042; 16412</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7998; 15901</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19078; 28860</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9630; 18192</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8604; 18102</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>12852; 22740</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>36971; 50905</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>16694; 28910</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18972; 32488</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>23564; 36428</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12291</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21147</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14839</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10073</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27594</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>24617</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>17486</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>39885</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>38788</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>39455</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>27559</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>7984; 18456</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>15653; 26919</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9770; 20606</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6035; 14287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>21315; 33325</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12695; 24075</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>18490; 30233</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>12241; 22534</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>32014; 48169</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>30607; 46725</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>31127; 48009</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>20633; 34016</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>34829</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>44599</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>30661</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>36404</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>47107</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>63751</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39850</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>55970</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>81937</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>108350</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>70510</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>92374</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>27295; 44369</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>35927; 52851</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>23791; 38828</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>27891; 45531</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>38235; 55173</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>55471; 72503</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>31591; 47403</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>44093; 68049</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>70226; 92929</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>94874; 121773</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>59104; 82089</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>79049; 106733</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>58735</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>60526</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>45185</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>30718</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>56821</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>69243</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>63874</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>50373</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>115556</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>129768</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>109059</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>81092</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>49591; 68313</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>51897; 69707</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>37104; 53136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>23523; 39612</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>48958; 65253</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>59767; 78458</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>54810; 73627</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>41595; 60549</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>102860; 128228</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>117077; 141561</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>96925; 121857</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>69050; 94689</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>203724</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>222166</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>189866</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>163002</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>254601</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>478715</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>503157</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>451038</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>417604</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>187155; 221822</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>201556; 239622</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>170642; 208172</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>138492; 185800</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>255946; 295496</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>260698; 298687</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>241033; 280406</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>229878; 282178</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>452143; 506013</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>475219; 527639</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>425364; 481685</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>380194; 453554</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 37,28</t>
+          <t>15,89; 35,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,29; 47,67</t>
+          <t>22,19; 47,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,19; 57,29</t>
+          <t>30,8; 56,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,45; 38,75</t>
+          <t>16,15; 41,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,09; 55,23</t>
+          <t>31,5; 54,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,13; 59,15</t>
+          <t>32,69; 58,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,09; 66,65</t>
+          <t>38,72; 65,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 35,2</t>
+          <t>15,12; 34,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 42,34</t>
+          <t>27,17; 42,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 50,36</t>
+          <t>31,73; 50,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,64; 58,42</t>
+          <t>39,2; 58,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 33,58</t>
+          <t>18,18; 34,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,67; 44,67</t>
+          <t>27,65; 45,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,0; 48,76</t>
+          <t>30,54; 49,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,95; 50,65</t>
+          <t>32,63; 50,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,22; 38,65</t>
+          <t>12,93; 38,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,78; 57,04</t>
+          <t>39,4; 56,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,62; 57,0</t>
+          <t>39,17; 57,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,5; 63,46</t>
+          <t>46,48; 63,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,2; 56,48</t>
+          <t>34,88; 57,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 48,94</t>
+          <t>36,5; 49,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,05; 50,12</t>
+          <t>36,85; 49,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,73; 54,48</t>
+          <t>42,22; 54,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,6; 43,73</t>
+          <t>24,18; 44,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 31,76</t>
+          <t>13,87; 30,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,29; 62,63</t>
+          <t>39,25; 62,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,7; 38,86</t>
+          <t>19,24; 39,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,26; 38,12</t>
+          <t>19,79; 39,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,75; 48,96</t>
+          <t>30,77; 49,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,11; 61,77</t>
+          <t>40,67; 62,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,37; 48,21</t>
+          <t>27,0; 48,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,68; 61,28</t>
+          <t>40,4; 62,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,39; 38,51</t>
+          <t>24,79; 39,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,83; 58,88</t>
+          <t>43,44; 58,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,34; 40,83</t>
+          <t>26,0; 40,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,18; 47,31</t>
+          <t>33,0; 47,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,48; 50,51</t>
+          <t>30,66; 50,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 41,74</t>
+          <t>20,9; 40,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,71; 48,71</t>
+          <t>27,17; 49,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,54; 41,9</t>
+          <t>16,14; 40,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,06; 48,58</t>
+          <t>31,06; 48,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,62; 64,56</t>
+          <t>41,73; 63,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,48; 60,51</t>
+          <t>37,52; 59,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 44,7</t>
+          <t>14,98; 46,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 46,28</t>
+          <t>33,34; 46,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,87; 50,12</t>
+          <t>33,53; 49,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,56; 51,99</t>
+          <t>35,28; 51,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 38,77</t>
+          <t>19,43; 40,81</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,07; 65,17</t>
+          <t>39,26; 65,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,08; 49,48</t>
+          <t>18,92; 49,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,9; 46,37</t>
+          <t>21,29; 47,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 47,15</t>
+          <t>24,11; 47,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,8; 72,32</t>
+          <t>49,1; 73,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,45; 61,3</t>
+          <t>32,67; 61,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,61; 47,57</t>
+          <t>24,14; 47,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 57,89</t>
+          <t>34,57; 59,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,28; 66,48</t>
+          <t>48,51; 66,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 51,61</t>
+          <t>30,66; 52,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,83; 44,23</t>
+          <t>26,03; 43,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,28; 49,9</t>
+          <t>32,18; 50,23</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,79; 36,5</t>
+          <t>15,84; 35,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,47; 57,56</t>
+          <t>32,8; 56,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,38; 42,97</t>
+          <t>20,86; 42,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,09; 35,73</t>
+          <t>15,68; 37,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,77; 60,61</t>
+          <t>40,26; 60,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,77; 48,87</t>
+          <t>25,39; 47,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,3; 60,98</t>
+          <t>37,84; 62,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,59; 47,11</t>
+          <t>26,18; 48,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,33; 45,64</t>
+          <t>30,66; 45,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,87; 48,66</t>
+          <t>32,1; 49,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,92; 49,23</t>
+          <t>33,12; 49,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,5; 38,74</t>
+          <t>23,69; 39,33</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,61; 38,37</t>
+          <t>23,15; 37,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,24; 47,43</t>
+          <t>32,28; 47,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,6; 36,88</t>
+          <t>23,0; 36,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,98; 42,42</t>
+          <t>25,58; 42,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,71; 47,2</t>
+          <t>32,1; 47,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,68; 62,32</t>
+          <t>46,58; 62,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,65; 41,49</t>
+          <t>27,7; 41,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,85; 50,7</t>
+          <t>33,12; 51,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,2; 39,97</t>
+          <t>30,14; 40,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41,65; 53,46</t>
+          <t>41,91; 53,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,92; 37,39</t>
+          <t>27,34; 37,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,73; 44,19</t>
+          <t>32,19; 43,96</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,94; 53,64</t>
+          <t>38,87; 52,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,65; 57,28</t>
+          <t>42,18; 57,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,67; 42,49</t>
+          <t>29,81; 43,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,44; 32,74</t>
+          <t>19,4; 32,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,67; 55,54</t>
+          <t>41,16; 55,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,79; 62,74</t>
+          <t>48,35; 62,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,93; 53,64</t>
+          <t>40,05; 52,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,92; 43,55</t>
+          <t>29,14; 43,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,01; 52,37</t>
+          <t>41,92; 52,34</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,45; 57,37</t>
+          <t>47,08; 57,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,95; 46,45</t>
+          <t>36,81; 46,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,55; 36,41</t>
+          <t>26,1; 36,29</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32,38; 38,37</t>
+          <t>32,24; 38,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38,24; 45,47</t>
+          <t>38,77; 45,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,34; 38,24</t>
+          <t>31,33; 38,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,07; 32,29</t>
+          <t>23,7; 32,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42,27; 48,81</t>
+          <t>41,92; 48,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,84; 53,66</t>
+          <t>47,09; 53,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,28; 48,02</t>
+          <t>41,36; 48,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35,21; 43,22</t>
+          <t>35,05; 42,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,2; 42,75</t>
+          <t>38,05; 42,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43,85; 48,69</t>
+          <t>43,8; 48,59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37,7; 42,69</t>
+          <t>37,46; 42,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,95; 36,93</t>
+          <t>30,92; 36,9</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8027; 17542</t>
+          <t>7478; 16661</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7770; 16617</t>
+          <t>7735; 16514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11480; 21082</t>
+          <t>11337; 20755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8787; 22038</t>
+          <t>9183; 23373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15604; 26855</t>
+          <t>15315; 26641</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13123; 24160</t>
+          <t>13353; 23917</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14541; 23586</t>
+          <t>13704; 23317</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9001; 21296</t>
+          <t>9146; 21113</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25543; 40505</t>
+          <t>25994; 40514</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23756; 38122</t>
+          <t>24020; 38228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27895; 42174</t>
+          <t>28296; 41959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20864; 39423</t>
+          <t>21347; 40607</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21465; 34651</t>
+          <t>21445; 34999</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22905; 36027</t>
+          <t>22568; 36323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27835; 42787</t>
+          <t>27568; 42559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14536; 45969</t>
+          <t>15373; 45280</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36957; 51700</t>
+          <t>35708; 51612</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30769; 45415</t>
+          <t>31205; 45950</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41949; 57241</t>
+          <t>41927; 57240</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39811; 63876</t>
+          <t>39450; 64674</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61988; 82316</t>
+          <t>61395; 82515</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56899; 76967</t>
+          <t>56588; 76032</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72899; 95172</t>
+          <t>73760; 94982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50111; 101471</t>
+          <t>56096; 102394</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7859; 18070</t>
+          <t>7891; 17340</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23930; 36294</t>
+          <t>22743; 36346</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10611; 22053</t>
+          <t>10922; 22603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9685; 19169</t>
+          <t>9954; 19630</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19949; 30762</t>
+          <t>19330; 31114</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24771; 37223</t>
+          <t>24504; 37445</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17503; 29741</t>
+          <t>16655; 29671</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22446; 34669</t>
+          <t>22854; 35374</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29208; 46113</t>
+          <t>29680; 46706</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51812; 69597</t>
+          <t>51351; 69054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31202; 48363</t>
+          <t>30795; 48232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34386; 50561</t>
+          <t>35260; 51236</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20890; 33515</t>
+          <t>20345; 33373</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11101; 22580</t>
+          <t>11305; 22024</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14603; 25669</t>
+          <t>14320; 26038</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7811; 19786</t>
+          <t>7621; 19273</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22269; 35993</t>
+          <t>23015; 36005</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23651; 35828</t>
+          <t>23156; 35438</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21547; 34786</t>
+          <t>21573; 34346</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7694; 27848</t>
+          <t>9335; 29221</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46742; 64995</t>
+          <t>46827; 65636</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37113; 54921</t>
+          <t>36742; 54321</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39181; 57285</t>
+          <t>38874; 56515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19635; 42465</t>
+          <t>21279; 44696</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13955; 23891</t>
+          <t>14395; 23894</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5289; 13034</t>
+          <t>4984; 13163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7042; 16412</t>
+          <t>7537; 16782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7998; 15901</t>
+          <t>8133; 15980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19078; 28860</t>
+          <t>19595; 29403</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9630; 18192</t>
+          <t>9695; 18357</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8604; 18102</t>
+          <t>9187; 18195</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12852; 22740</t>
+          <t>13581; 23403</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36971; 50905</t>
+          <t>37144; 50794</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16694; 28910</t>
+          <t>17174; 29195</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18972; 32488</t>
+          <t>19115; 31960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23564; 36428</t>
+          <t>23496; 36670</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7984; 18456</t>
+          <t>8008; 17842</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15653; 26919</t>
+          <t>15340; 26303</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9770; 20606</t>
+          <t>10002; 20611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6035; 14287</t>
+          <t>6270; 14892</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21315; 33325</t>
+          <t>22136; 33350</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12695; 24075</t>
+          <t>12506; 23496</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18490; 30233</t>
+          <t>18757; 30860</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12241; 22534</t>
+          <t>12520; 23434</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32014; 48169</t>
+          <t>32356; 48015</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30607; 46725</t>
+          <t>30822; 47231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31127; 48009</t>
+          <t>32301; 48370</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20633; 34016</t>
+          <t>20799; 34535</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>27295; 44369</t>
+          <t>26768; 42968</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35927; 52851</t>
+          <t>35975; 53029</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23791; 38828</t>
+          <t>24215; 38862</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27891; 45531</t>
+          <t>27463; 45356</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38235; 55173</t>
+          <t>37522; 55639</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55471; 72503</t>
+          <t>54189; 72521</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31591; 47403</t>
+          <t>31653; 47555</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44093; 68049</t>
+          <t>44444; 68601</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70226; 92929</t>
+          <t>70071; 94373</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94874; 121773</t>
+          <t>95467; 121168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59104; 82089</t>
+          <t>60013; 82330</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>79049; 106733</t>
+          <t>77762; 106198</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49591; 68313</t>
+          <t>49511; 67168</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51897; 69707</t>
+          <t>51329; 70313</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37104; 53136</t>
+          <t>37281; 54134</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23523; 39612</t>
+          <t>23471; 39370</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>48958; 65253</t>
+          <t>48368; 65750</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59767; 78458</t>
+          <t>60467; 78112</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54810; 73627</t>
+          <t>54977; 72740</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>41595; 60549</t>
+          <t>40511; 60683</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>102860; 128228</t>
+          <t>102633; 128151</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>117077; 141561</t>
+          <t>116156; 142206</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96925; 121857</t>
+          <t>96554; 122866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>69050; 94689</t>
+          <t>67882; 94355</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>187155; 221822</t>
+          <t>186354; 221172</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>201556; 239622</t>
+          <t>204318; 242337</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>170642; 208172</t>
+          <t>170586; 208083</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138492; 185800</t>
+          <t>136345; 185752</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>255946; 295496</t>
+          <t>253811; 293625</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>260698; 298687</t>
+          <t>262113; 300282</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>241033; 280406</t>
+          <t>241538; 281183</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>229878; 282178</t>
+          <t>228801; 279715</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>452143; 506013</t>
+          <t>450305; 505438</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>475219; 527639</t>
+          <t>474635; 526569</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>425364; 481685</t>
+          <t>422726; 477154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>380194; 453554</t>
+          <t>379725; 453220</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42,54%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45,36%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53,98%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24,55%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25,49%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34,49%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>44,18%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,89; 35,41</t>
+          <t>30,11; 53,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,19; 47,38</t>
+          <t>31,34; 57,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,8; 56,4</t>
+          <t>40,31; 66,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 41,09</t>
+          <t>16,31; 36,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,5; 54,79</t>
+          <t>17,21; 36,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,69; 58,55</t>
+          <t>24,06; 49,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,72; 65,89</t>
+          <t>31,78; 57,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,12; 34,89</t>
+          <t>17,11; 38,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,17; 42,35</t>
+          <t>26,09; 41,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,73; 50,5</t>
+          <t>31,95; 50,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,2; 58,12</t>
+          <t>39,51; 58,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,18; 34,59</t>
+          <t>19,15; 33,12</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54,92%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>35,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>39,61%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>41,31%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>47,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>54,92%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,65; 45,12</t>
+          <t>40,54; 57,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,54; 49,16</t>
+          <t>38,32; 56,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,63; 50,38</t>
+          <t>46,0; 63,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 38,07</t>
+          <t>34,78; 56,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,4; 56,94</t>
+          <t>26,91; 45,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,17; 57,67</t>
+          <t>30,13; 49,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,48; 63,45</t>
+          <t>32,95; 50,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,88; 57,18</t>
+          <t>22,96; 39,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,5; 49,06</t>
+          <t>37,04; 48,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 49,51</t>
+          <t>37,08; 49,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,22; 54,37</t>
+          <t>42,34; 54,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,18; 44,13</t>
+          <t>31,78; 46,15</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50,75%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>21,38%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>51,32%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28,72%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>39,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 30,47</t>
+          <t>29,78; 48,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,25; 62,72</t>
+          <t>40,65; 61,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,24; 39,83</t>
+          <t>26,63; 47,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,79; 39,03</t>
+          <t>39,9; 63,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,77; 49,52</t>
+          <t>12,57; 31,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,67; 62,14</t>
+          <t>40,53; 62,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,0; 48,1</t>
+          <t>19,3; 40,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,4; 62,53</t>
+          <t>19,5; 38,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,79; 39,01</t>
+          <t>24,98; 37,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,44; 58,42</t>
+          <t>43,07; 58,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,0; 40,72</t>
+          <t>26,66; 41,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,0; 47,95</t>
+          <t>32,72; 47,02</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>40,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29,9%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>37,83%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,4%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,66; 50,3</t>
+          <t>29,95; 48,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 40,72</t>
+          <t>42,0; 64,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,17; 49,41</t>
+          <t>36,12; 59,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,14; 40,82</t>
+          <t>16,17; 47,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,06; 48,6</t>
+          <t>32,34; 50,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,73; 63,86</t>
+          <t>20,59; 40,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,52; 59,74</t>
+          <t>27,32; 49,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 46,9</t>
+          <t>15,51; 40,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,34; 46,74</t>
+          <t>32,66; 45,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,53; 49,57</t>
+          <t>34,42; 49,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,28; 51,29</t>
+          <t>34,98; 50,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 40,81</t>
+          <t>19,6; 40,24</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61,51%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34,71%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>47,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>52,21%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>33,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,99%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,26; 65,18</t>
+          <t>47,31; 74,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,92; 49,97</t>
+          <t>31,95; 62,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,29; 47,42</t>
+          <t>22,42; 47,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,11; 47,38</t>
+          <t>35,72; 60,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,1; 73,68</t>
+          <t>40,15; 66,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,67; 61,85</t>
+          <t>18,47; 50,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,14; 47,81</t>
+          <t>21,98; 47,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,57; 59,58</t>
+          <t>23,3; 44,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,51; 66,34</t>
+          <t>47,0; 66,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,66; 52,11</t>
+          <t>29,34; 51,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,03; 43,51</t>
+          <t>25,51; 43,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,18; 50,23</t>
+          <t>32,86; 49,33</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35,81%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49,65%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35,72%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>24,31%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>45,21%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>30,95%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>50,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,65%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,84; 35,29</t>
+          <t>39,24; 60,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,8; 56,24</t>
+          <t>24,66; 47,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,86; 42,98</t>
+          <t>37,32; 61,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,68; 37,25</t>
+          <t>25,91; 48,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,26; 60,65</t>
+          <t>15,91; 34,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,39; 47,7</t>
+          <t>33,1; 57,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,84; 62,25</t>
+          <t>20,68; 43,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,18; 48,99</t>
+          <t>15,88; 37,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,66; 45,49</t>
+          <t>30,7; 45,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,1; 49,18</t>
+          <t>32,65; 49,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,12; 49,6</t>
+          <t>32,03; 48,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,69; 39,33</t>
+          <t>22,3; 38,65</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54,8%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34,88%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>30,12%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>40,02%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>29,12%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,15; 37,16</t>
+          <t>32,8; 46,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,28; 47,59</t>
+          <t>47,25; 62,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,0; 36,91</t>
+          <t>28,16; 43,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,58; 42,25</t>
+          <t>33,75; 51,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,1; 47,6</t>
+          <t>23,69; 37,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,58; 62,33</t>
+          <t>32,84; 47,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,7; 41,62</t>
+          <t>21,9; 36,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,12; 51,11</t>
+          <t>25,8; 40,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,14; 40,59</t>
+          <t>30,43; 40,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41,91; 53,2</t>
+          <t>42,21; 53,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,34; 37,5</t>
+          <t>27,14; 36,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,19; 43,96</t>
+          <t>32,27; 44,43</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>48,36%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>55,37%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>35,92%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>46,12%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>49,74%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>36,14%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>25,39%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>46,53%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,87; 52,74</t>
+          <t>41,31; 55,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,18; 57,78</t>
+          <t>48,03; 62,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,81; 43,29</t>
+          <t>39,94; 53,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,4; 32,54</t>
+          <t>29,0; 43,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,16; 55,96</t>
+          <t>38,86; 53,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,35; 62,46</t>
+          <t>42,23; 56,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,05; 52,99</t>
+          <t>29,49; 43,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,14; 43,64</t>
+          <t>18,1; 31,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41,92; 52,34</t>
+          <t>41,96; 51,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,08; 57,63</t>
+          <t>47,46; 57,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,81; 46,84</t>
+          <t>36,43; 46,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,1; 36,29</t>
+          <t>25,38; 35,67</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>50,48%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>50,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32,24; 38,26</t>
+          <t>42,26; 48,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38,77; 45,98</t>
+          <t>46,95; 54,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,33; 38,22</t>
+          <t>41,18; 48,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23,7; 32,28</t>
+          <t>35,32; 43,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41,92; 48,5</t>
+          <t>32,29; 38,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,09; 53,95</t>
+          <t>38,97; 45,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,36; 48,15</t>
+          <t>31,75; 38,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35,05; 42,85</t>
+          <t>25,56; 31,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,05; 42,71</t>
+          <t>38,08; 42,61</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43,8; 48,59</t>
+          <t>43,86; 49,11</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37,46; 42,29</t>
+          <t>37,54; 42,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,92; 36,9</t>
+          <t>31,8; 36,74</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20686</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18529</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19102</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12018</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11994</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>12022</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>16259</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15067</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20686</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18529</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19102</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>23940</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7478; 16661</t>
+          <t>14640; 26083</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7735; 16514</t>
+          <t>12803; 23444</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11337; 20755</t>
+          <t>14265; 23588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9183; 23373</t>
+          <t>7985; 18065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15315; 26641</t>
+          <t>8097; 17333</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13353; 23917</t>
+          <t>8388; 17096</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13704; 23317</t>
+          <t>11696; 21124</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9146; 21113</t>
+          <t>7616; 17189</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25994; 40514</t>
+          <t>24959; 39673</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24020; 38228</t>
+          <t>24186; 38194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28296; 41959</t>
+          <t>28524; 42247</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21347; 40607</t>
+          <t>17894; 30957</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37465</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49545</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46708</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27667</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>29267</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>34901</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31514</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>44379</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37465</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49545</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50991</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>75559</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21445; 34999</t>
+          <t>36745; 51698</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22568; 36323</t>
+          <t>30533; 44841</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27568; 42559</t>
+          <t>41495; 57298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15373; 45280</t>
+          <t>36015; 58324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35708; 51612</t>
+          <t>20870; 35175</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31205; 45950</t>
+          <t>22263; 36734</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41927; 57240</t>
+          <t>27835; 42348</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39450; 64674</t>
+          <t>21288; 36704</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61395; 82515</t>
+          <t>62299; 82049</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56588; 76032</t>
+          <t>56940; 76553</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73760; 94982</t>
+          <t>73961; 95445</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56096; 102394</t>
+          <t>62365; 90572</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>24979</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30677</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23156</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25636</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>12166</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>29742</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>16297</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14231</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>24979</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30677</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>23156</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42961</t>
+          <t>39584</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7891; 17340</t>
+          <t>18708; 30642</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22743; 36346</t>
+          <t>24492; 36914</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10922; 22603</t>
+          <t>16427; 29263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9954; 19630</t>
+          <t>20154; 31835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19330; 31114</t>
+          <t>7154; 17673</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24504; 37445</t>
+          <t>23489; 36487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16655; 29671</t>
+          <t>10954; 22937</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22854; 35374</t>
+          <t>9634; 19011</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29680; 46706</t>
+          <t>29912; 44777</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51351; 69054</t>
+          <t>50917; 68770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30795; 48232</t>
+          <t>31580; 48842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35260; 51236</t>
+          <t>32696; 46983</t>
         </is>
       </c>
     </row>
@@ -2702,32 +2702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28875</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29587</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17984</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26901</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>16172</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19937</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13195</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>28875</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29587</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27822</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31850</t>
+          <t>30840</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20345; 33373</t>
+          <t>22189; 35821</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11305; 22024</t>
+          <t>23310; 35724</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14320; 26038</t>
+          <t>20764; 34102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7621; 19273</t>
+          <t>9455; 27567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23015; 36005</t>
+          <t>21457; 33333</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23156; 35438</t>
+          <t>11136; 21961</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21573; 34346</t>
+          <t>14399; 25887</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9335; 29221</t>
+          <t>7501; 19394</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46827; 65636</t>
+          <t>45868; 64467</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36742; 54321</t>
+          <t>37721; 54091</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38874; 56515</t>
+          <t>38547; 56171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21279; 44696</t>
+          <t>20937; 42984</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24549</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14097</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13207</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>19142</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>8692</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>11786</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11799</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24549</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14097</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13207</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>29905</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14395; 23894</t>
+          <t>18882; 29537</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4984; 13163</t>
+          <t>9481; 18428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7537; 16782</t>
+          <t>8532; 18046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8133; 15980</t>
+          <t>13660; 23144</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19595; 29403</t>
+          <t>14719; 24295</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9695; 18357</t>
+          <t>4864; 13181</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9187; 18195</t>
+          <t>7780; 16774</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13581; 23403</t>
+          <t>8124; 15660</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37144; 50794</t>
+          <t>35990; 50958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17174; 29195</t>
+          <t>16434; 28993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19115; 31960</t>
+          <t>18738; 32058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23496; 36670</t>
+          <t>24020; 36060</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27594</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24617</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>15198</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12291</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>21147</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>14839</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10073</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>27594</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17642</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24617</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>25267</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8008; 17842</t>
+          <t>21576; 33240</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15340; 26303</t>
+          <t>12148; 23634</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10002; 20611</t>
+          <t>18500; 30494</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6270; 14892</t>
+          <t>11025; 20818</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22136; 33350</t>
+          <t>8043; 17611</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12506; 23496</t>
+          <t>15482; 26827</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18757; 30860</t>
+          <t>9915; 21014</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12520; 23434</t>
+          <t>6446; 15252</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32356; 48015</t>
+          <t>32399; 48517</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30822; 47231</t>
+          <t>31353; 47329</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32301; 48370</t>
+          <t>31241; 47485</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20799; 34535</t>
+          <t>18542; 32136</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>47107</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>63751</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>39850</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>52637</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>34829</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>44599</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>30661</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>36404</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47107</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>63751</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>39850</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>55970</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92374</t>
+          <t>87385</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>26768; 42968</t>
+          <t>38337; 54881</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35975; 53029</t>
+          <t>54969; 72819</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24215; 38862</t>
+          <t>32173; 49155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27463; 45356</t>
+          <t>41702; 64173</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37522; 55639</t>
+          <t>27391; 43390</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>54189; 72521</t>
+          <t>36594; 53381</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31653; 47555</t>
+          <t>23054; 38648</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44444; 68601</t>
+          <t>27143; 42746</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70071; 94373</t>
+          <t>70756; 94084</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95467; 121168</t>
+          <t>96148; 120763</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60013; 82330</t>
+          <t>59573; 81176</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>77762; 106198</t>
+          <t>73813; 101645</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>56821</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>69243</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>63874</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>50826</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>58735</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>60526</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>45185</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>30718</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>56821</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>69243</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>63874</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>50373</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81092</t>
+          <t>82142</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49511; 67168</t>
+          <t>48537; 65341</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51329; 70313</t>
+          <t>60067; 78544</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37281; 54134</t>
+          <t>54826; 73828</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23471; 39370</t>
+          <t>41033; 61684</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>48368; 65750</t>
+          <t>49491; 68174</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60467; 78112</t>
+          <t>51388; 68944</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54977; 72740</t>
+          <t>36871; 53856</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>40511; 60683</t>
+          <t>23392; 40497</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>102633; 128151</t>
+          <t>102735; 126833</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>116156; 142206</t>
+          <t>117106; 142324</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96554; 122866</t>
+          <t>95570; 120767</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>67882; 94355</t>
+          <t>68699; 96559</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>234</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>239119</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>203724</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>222166</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>189866</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>163002</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>274990</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>280991</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>261173</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>155504</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>417604</t>
+          <t>394622</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>186354; 221172</t>
+          <t>255865; 293526</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>204318; 242337</t>
+          <t>261343; 301978</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>170586; 208083</t>
+          <t>240456; 281764</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136345; 185752</t>
+          <t>214496; 262239</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>253811; 293625</t>
+          <t>186635; 223096</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>262113; 300282</t>
+          <t>205399; 240883</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>241538; 281183</t>
+          <t>172831; 207961</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>228801; 279715</t>
+          <t>139280; 173325</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>450305; 505438</t>
+          <t>450692; 504253</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>474635; 526569</t>
+          <t>475291; 532153</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>422726; 477154</t>
+          <t>423582; 476396</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>379725; 453220</t>
+          <t>366438; 423257</t>
         </is>
       </c>
     </row>
